--- a/data/trans_bre/P16A06-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A06-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 3,66</t>
+          <t>-1,36; 3,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 4,54</t>
+          <t>-0,93; 4,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 3,12</t>
+          <t>-2,12; 3,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 3,08</t>
+          <t>-2,04; 3,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-48,09; 298,34</t>
+          <t>-51,11; 283,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-44,5; 419,95</t>
+          <t>-40,91; 442,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-52,54; 206,05</t>
+          <t>-54,41; 207,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-29,17; 76,83</t>
+          <t>-30,1; 80,69</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 2,03</t>
+          <t>-2,1; 2,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 2,18</t>
+          <t>-2,7; 1,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,66</t>
+          <t>-1,03; 3,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 6,52</t>
+          <t>0,85; 6,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-76,76; 221,45</t>
+          <t>-76,96; 212,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-71,09; 203,36</t>
+          <t>-76,0; 179,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,25; 318,94</t>
+          <t>-39,01; 314,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,28; 213,59</t>
+          <t>13,4; 217,47</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 6,35</t>
+          <t>0,09; 6,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 4,98</t>
+          <t>-0,98; 5,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 12,17</t>
+          <t>1,92; 12,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,56; 14,48</t>
+          <t>4,81; 14,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 773,07</t>
+          <t>-9,57; 672,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-30,21; 205,1</t>
+          <t>-31,46; 227,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61,58; 742,05</t>
+          <t>52,86; 696,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>69,58; 955,67</t>
+          <t>78,41; 1265,45</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 2,68</t>
+          <t>-0,62; 2,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,32</t>
+          <t>1,06; 4,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 4,22</t>
+          <t>0,58; 4,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 2,2</t>
+          <t>-3,69; 2,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 143,55</t>
+          <t>-21,92; 134,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,01; 382,2</t>
+          <t>38,14; 385,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 175,11</t>
+          <t>12,47; 187,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,7; 39,92</t>
+          <t>-51,67; 38,68</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 3,01</t>
+          <t>-1,75; 3,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 8,99</t>
+          <t>4,12; 8,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,33; 9,56</t>
+          <t>4,36; 10,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,37; 12,1</t>
+          <t>4,41; 12,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-45,32; 188,4</t>
+          <t>-42,84; 174,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>118,8; 724,62</t>
+          <t>104,24; 658,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>104,9; 452,58</t>
+          <t>96,02; 485,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>68,98; 293,03</t>
+          <t>66,19; 294,04</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,66; 7,28</t>
+          <t>4,46; 7,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,92; 10,58</t>
+          <t>6,96; 10,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,2; 11,67</t>
+          <t>7,15; 11,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,28; 12,25</t>
+          <t>3,67; 12,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>272,61; —</t>
+          <t>293,58; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,1; 912,03</t>
+          <t>29,79; 972,48</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,13</t>
+          <t>1,41; 3,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,32; 5,37</t>
+          <t>3,35; 5,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,9; 6,02</t>
+          <t>3,78; 5,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,54</t>
+          <t>3,01; 6,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>57,72; 193,85</t>
+          <t>59,64; 190,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>136,16; 328,59</t>
+          <t>137,77; 326,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>123,14; 268,51</t>
+          <t>122,48; 258,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>59,22; 167,22</t>
+          <t>59,04; 160,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A06-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A06-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 3,56</t>
+          <t>-1,07; 3,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 4,67</t>
+          <t>-0,75; 4,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 3,22</t>
+          <t>-2,06; 3,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 3,17</t>
+          <t>-1,7; 3,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-51,11; 283,04</t>
+          <t>-47,92; 284,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-40,91; 442,33</t>
+          <t>-37,7; 523,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-54,41; 207,18</t>
+          <t>-55,97; 212,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-30,1; 80,69</t>
+          <t>-28,82; 96,67</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,73</t>
+          <t>3,85</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>93,42%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 2,09</t>
+          <t>-2,41; 1,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 1,87</t>
+          <t>-2,89; 1,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 3,73</t>
+          <t>-0,99; 3,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 6,52</t>
+          <t>1,11; 6,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-76,96; 212,54</t>
+          <t>-78,8; 188,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-76,0; 179,17</t>
+          <t>-79,36; 215,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,01; 314,3</t>
+          <t>-37,44; 293,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,4; 217,47</t>
+          <t>19,44; 229,61</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,59</t>
+          <t>6,1</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>230,1%</t>
+          <t>104,73%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 6,03</t>
+          <t>0,1; 6,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 5,31</t>
+          <t>-0,97; 5,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 12,05</t>
+          <t>1,98; 11,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,81; 14,79</t>
+          <t>2,34; 10,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 672,56</t>
+          <t>-2,27; 751,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,46; 227,88</t>
+          <t>-24,67; 213,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,86; 696,99</t>
+          <t>62,54; 717,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>78,41; 1265,45</t>
+          <t>27,95; 226,88</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>1,27</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-2,87%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 2,68</t>
+          <t>-0,57; 2,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,42</t>
+          <t>1,0; 4,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,46</t>
+          <t>0,4; 4,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 2,16</t>
+          <t>-0,59; 3,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,92; 134,57</t>
+          <t>-22,09; 137,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,14; 385,51</t>
+          <t>40,76; 412,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,47; 187,11</t>
+          <t>6,31; 161,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-51,67; 38,68</t>
+          <t>-8,85; 63,77</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,79</t>
+          <t>9,94</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>155,9%</t>
+          <t>189,29%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 3,1</t>
+          <t>-1,81; 3,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,12; 8,66</t>
+          <t>4,14; 9,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,36; 10,06</t>
+          <t>4,31; 9,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,41; 12,45</t>
+          <t>7,2; 12,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-42,84; 174,29</t>
+          <t>-42,68; 202,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>104,24; 658,53</t>
+          <t>113,7; 772,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,02; 485,95</t>
+          <t>97,78; 502,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>66,19; 294,04</t>
+          <t>98,14; 343,72</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9,51</t>
+          <t>8,82</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>282,54%</t>
+          <t>230,37%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,09</t>
+          <t>4,58; 7,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,96; 10,52</t>
+          <t>6,84; 10,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,15; 11,61</t>
+          <t>7,18; 11,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,67; 12,48</t>
+          <t>3,6; 11,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>293,58; —</t>
+          <t>274,96; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29,79; 972,48</t>
+          <t>12,16; 640,47</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,92</t>
+          <t>5,2</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,08</t>
+          <t>1,35; 3,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,26</t>
+          <t>3,34; 5,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,78; 5,98</t>
+          <t>3,75; 5,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,01; 6,53</t>
+          <t>4,14; 6,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>59,64; 190,23</t>
+          <t>54,6; 184,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>137,77; 326,46</t>
+          <t>133,29; 327,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>122,48; 258,86</t>
+          <t>122,32; 265,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>59,04; 160,58</t>
+          <t>70,77; 135,07</t>
         </is>
       </c>
     </row>
